--- a/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/PMCCS/Pol Mandated Cap Const Sched.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\DE\elec\PMCCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\Delaware\DE-eps\InputData\elec\PMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{006E6902-E45C-4181-9791-F60613CCC75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F25EC04-E307-47F6-ACA1-DC7276E66B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9030" yWindow="2700" windowWidth="17580" windowHeight="12240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="PMCCS" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="PMCCS" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="131">
   <si>
     <t>PMCCS Policy Mandated Capacity Construction Schedule</t>
   </si>
@@ -413,6 +414,18 @@
   </si>
   <si>
     <t>Wyoming</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>distpv_MW</t>
+  </si>
+  <si>
+    <t>upv_MW</t>
+  </si>
+  <si>
+    <t>ADDED</t>
   </si>
 </sst>
 </file>
@@ -451,12 +464,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -471,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -479,6 +498,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,9 +838,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +857,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="str">
         <f>LOOKUP(B1,F2:G51,G2:G51)</f>
         <v>DE</v>
@@ -849,7 +869,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -863,7 +883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F4" s="4" t="s">
         <v>79</v>
       </c>
@@ -871,7 +891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -882,7 +902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -893,7 +913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -904,7 +924,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -915,7 +935,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -926,7 +946,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F10" s="4" t="s">
         <v>85</v>
       </c>
@@ -934,7 +954,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F11" s="4" t="s">
         <v>86</v>
       </c>
@@ -942,7 +962,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -953,7 +973,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F13" s="4" t="s">
         <v>88</v>
       </c>
@@ -961,7 +981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F14" s="4" t="s">
         <v>89</v>
       </c>
@@ -969,7 +989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F15" s="4" t="s">
         <v>90</v>
       </c>
@@ -977,7 +997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F16" s="4" t="s">
         <v>91</v>
       </c>
@@ -985,7 +1005,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F17" s="4" t="s">
         <v>92</v>
       </c>
@@ -993,7 +1013,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F18" s="4" t="s">
         <v>93</v>
       </c>
@@ -1001,7 +1021,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F19" s="4" t="s">
         <v>94</v>
       </c>
@@ -1009,7 +1029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F20" s="4" t="s">
         <v>95</v>
       </c>
@@ -1017,7 +1037,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F21" s="4" t="s">
         <v>96</v>
       </c>
@@ -1025,7 +1045,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F22" s="4" t="s">
         <v>97</v>
       </c>
@@ -1033,7 +1053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F23" s="4" t="s">
         <v>98</v>
       </c>
@@ -1041,7 +1061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F24" s="4" t="s">
         <v>99</v>
       </c>
@@ -1049,7 +1069,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F25" s="4" t="s">
         <v>100</v>
       </c>
@@ -1057,7 +1077,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F26" s="4" t="s">
         <v>101</v>
       </c>
@@ -1065,7 +1085,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F27" s="4" t="s">
         <v>102</v>
       </c>
@@ -1073,7 +1093,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F28" s="4" t="s">
         <v>103</v>
       </c>
@@ -1081,7 +1101,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F29" s="4" t="s">
         <v>104</v>
       </c>
@@ -1089,7 +1109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F30" s="4" t="s">
         <v>105</v>
       </c>
@@ -1097,7 +1117,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F31" s="4" t="s">
         <v>106</v>
       </c>
@@ -1105,7 +1125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F32" s="4" t="s">
         <v>107</v>
       </c>
@@ -1113,7 +1133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F33" s="4" t="s">
         <v>108</v>
       </c>
@@ -1121,7 +1141,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F34" s="4" t="s">
         <v>109</v>
       </c>
@@ -1129,7 +1149,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F35" s="4" t="s">
         <v>110</v>
       </c>
@@ -1137,7 +1157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F36" s="4" t="s">
         <v>111</v>
       </c>
@@ -1145,7 +1165,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F37" s="4" t="s">
         <v>112</v>
       </c>
@@ -1153,7 +1173,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F38" s="4" t="s">
         <v>113</v>
       </c>
@@ -1161,7 +1181,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F39" s="4" t="s">
         <v>114</v>
       </c>
@@ -1169,7 +1189,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F40" s="4" t="s">
         <v>115</v>
       </c>
@@ -1177,7 +1197,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F41" s="4" t="s">
         <v>116</v>
       </c>
@@ -1185,7 +1205,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F42" s="4" t="s">
         <v>117</v>
       </c>
@@ -1193,7 +1213,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F43" s="4" t="s">
         <v>118</v>
       </c>
@@ -1201,7 +1221,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F44" s="4" t="s">
         <v>119</v>
       </c>
@@ -1209,7 +1229,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F45" s="4" t="s">
         <v>120</v>
       </c>
@@ -1217,7 +1237,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F46" s="4" t="s">
         <v>121</v>
       </c>
@@ -1225,7 +1245,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F47" s="4" t="s">
         <v>122</v>
       </c>
@@ -1233,7 +1253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F48" s="4" t="s">
         <v>123</v>
       </c>
@@ -1241,7 +1261,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="4" t="s">
         <v>124</v>
       </c>
@@ -1249,7 +1269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F50" s="4" t="s">
         <v>125</v>
       </c>
@@ -1257,7 +1277,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F51" s="4" t="s">
         <v>126</v>
       </c>
@@ -1272,17 +1292,377 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0FC8627-44A0-4269-A048-09CFBEB4C935}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1">
+        <v>36.199999999999903</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2">
+        <v>125.9</v>
+      </c>
+      <c r="C2">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="D2">
+        <v>2023</v>
+      </c>
+      <c r="E2">
+        <f>SUM(B2:C2)</f>
+        <v>162.10000000000002</v>
+      </c>
+      <c r="F2">
+        <f>E2-E1</f>
+        <v>125.90000000000012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3">
+        <v>178.4</v>
+      </c>
+      <c r="C3">
+        <v>86.2</v>
+      </c>
+      <c r="D3">
+        <v>2024</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E16" si="0">SUM(B3:C3)</f>
+        <v>264.60000000000002</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F16" si="1">E3-E2</f>
+        <v>102.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4">
+        <v>246.4</v>
+      </c>
+      <c r="C4">
+        <v>86.2</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>332.6</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5">
+        <v>333.4</v>
+      </c>
+      <c r="C5">
+        <v>86.2</v>
+      </c>
+      <c r="D5">
+        <v>2028</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>419.59999999999997</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>86.999999999999943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6">
+        <v>408.4</v>
+      </c>
+      <c r="C6">
+        <v>86.5</v>
+      </c>
+      <c r="D6">
+        <v>2030</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>494.9</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>75.300000000000011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7">
+        <v>466.2</v>
+      </c>
+      <c r="C7">
+        <v>86.8</v>
+      </c>
+      <c r="D7">
+        <v>2032</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>553</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>58.100000000000023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8">
+        <v>493.7</v>
+      </c>
+      <c r="C8">
+        <v>86.8</v>
+      </c>
+      <c r="D8">
+        <v>2034</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>580.5</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9">
+        <v>498.4</v>
+      </c>
+      <c r="C9">
+        <v>86.8</v>
+      </c>
+      <c r="D9">
+        <v>2036</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>585.19999999999993</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>4.6999999999999318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10">
+        <v>502.3</v>
+      </c>
+      <c r="C10">
+        <v>86.8</v>
+      </c>
+      <c r="D10">
+        <v>2038</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>589.1</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>3.9000000000000909</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11">
+        <v>506.2</v>
+      </c>
+      <c r="C11">
+        <v>86.8</v>
+      </c>
+      <c r="D11">
+        <v>2040</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>593</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>3.8999999999999773</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12">
+        <v>517.70000000000005</v>
+      </c>
+      <c r="C12">
+        <v>62.5</v>
+      </c>
+      <c r="D12">
+        <v>2042</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>580.20000000000005</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13">
+        <v>532.20000000000005</v>
+      </c>
+      <c r="C13">
+        <v>58.6</v>
+      </c>
+      <c r="D13">
+        <v>2044</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>590.80000000000007</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>10.600000000000023</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14">
+        <v>537.20000000000005</v>
+      </c>
+      <c r="C14">
+        <v>57.4</v>
+      </c>
+      <c r="D14">
+        <v>2046</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>594.6</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>3.7999999999999545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15">
+        <v>550.20000000000005</v>
+      </c>
+      <c r="C15">
+        <v>53.6</v>
+      </c>
+      <c r="D15">
+        <v>2048</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>603.80000000000007</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>9.2000000000000455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16">
+        <v>568.4</v>
+      </c>
+      <c r="C16">
+        <v>50.6</v>
+      </c>
+      <c r="D16">
+        <v>2050</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>619</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>15.199999999999932</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.6328125" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1383,7 +1763,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1585,7 +1965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1787,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1888,7 +2268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1896,100 +2276,128 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!F1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>125.90000000000012</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!G1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>102.5</v>
       </c>
       <c r="H7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!H1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!I1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>68</v>
       </c>
       <c r="J7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!J1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!K1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>86.999999999999943</v>
       </c>
       <c r="L7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!L1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!M1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>75.300000000000011</v>
       </c>
       <c r="N7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!N1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!O1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>58.100000000000023</v>
       </c>
       <c r="P7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!P1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!Q1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>27.5</v>
       </c>
       <c r="R7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!R1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!S1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>4.6999999999999318</v>
       </c>
       <c r="T7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!T1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!U1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>3.9000000000000909</v>
       </c>
       <c r="V7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!V1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!W1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>3.8999999999999773</v>
       </c>
       <c r="X7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!X1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="Y7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!Y1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="Z7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!Z1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AA1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>10.600000000000023</v>
       </c>
       <c r="AB7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AB1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AC1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>3.7999999999999545</v>
       </c>
       <c r="AD7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AD1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AE1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>9.2000000000000455</v>
       </c>
       <c r="AF7">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AF1,Sheet1!$D$2:$D$16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+        <f>IFERROR(INDEX(Sheet1!$F$2:$F$16,MATCH(PMCCS!AG1,Sheet1!$D$2:$D$16,0)),0)</f>
+        <v>15.199999999999932</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2090,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2101,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2191,7 +2599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2292,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2393,7 +2801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2401,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>44.400000000000006</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2494,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2595,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2696,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2797,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -2898,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
